--- a/test-fixtures/e2e/FIRMA-C ENTEGRE SAHA-UC - Yangın Tesisatı.xlsx
+++ b/test-fixtures/e2e/FIRMA-C ENTEGRE SAHA-UC - Yangın Tesisatı.xlsx
@@ -3858,7 +3858,7 @@
     <t>Aksesuar : Kapı Üzeri Elle Kumandalı Menfez (30x30 cm)</t>
   </si>
   <si>
-    <t>HASAN SEVİNDİK</t>
+    <t>KİŞİ-ANONİM</t>
   </si>
   <si>
     <t>YANGIN TESİSATI</t>
